--- a/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.02646283221782112</v>
+        <v>0.08111468452155768</v>
       </c>
       <c r="B2">
-        <v>0.09810895849634738</v>
+        <v>0.1762049193244267</v>
       </c>
       <c r="C2">
-        <v>0.1631255253841821</v>
+        <v>0.2621732842183989</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.08111468452155768</v>
+        <v>0.08106053498780161</v>
       </c>
       <c r="B2">
-        <v>0.1762049193244267</v>
+        <v>0.1733155449500715</v>
       </c>
       <c r="C2">
-        <v>0.2621732842183989</v>
+        <v>0.2567212372259388</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.08106053498780161</v>
+        <v>0.07802021469623809</v>
       </c>
       <c r="B2">
-        <v>0.1733155449500715</v>
+        <v>0.1733992931025511</v>
       </c>
       <c r="C2">
-        <v>0.2567212372259388</v>
+        <v>0.2596279833619916</v>
       </c>
       <c r="D2">
         <v>1</v>
